--- a/data/Caja.xlsx
+++ b/data/Caja.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CajaWeb\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75B522C-921B-43B3-B48F-3A844DEBAAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D1852B-E405-4D81-9AC0-75DA85E872A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,13 +164,13 @@
     <t>°</t>
   </si>
   <si>
-    <t>ESTEBAN</t>
-  </si>
-  <si>
     <t>Saldo inicial de caja Ingreso de Caja Efectivo USD</t>
   </si>
   <si>
     <t>Saldo inicial de caja Ingreso de Caja Efectivo $</t>
+  </si>
+  <si>
+    <t>ESTEBAN TALLAC</t>
   </si>
 </sst>
 </file>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="49">
         <v>46094</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="28">
         <v>3922100</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="27">
         <v>5</v>

--- a/data/Caja.xlsx
+++ b/data/Caja.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CajaWeb\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D1852B-E405-4D81-9AC0-75DA85E872A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0F6738-1C56-4200-B949-530B10F7BF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
   <si>
     <t>FECHA</t>
   </si>
@@ -110,9 +110,6 @@
     <t xml:space="preserve">MERCADO LIBRE </t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL LOCAL </t>
-  </si>
-  <si>
     <t xml:space="preserve">LOCAL EN EFECTIVO </t>
   </si>
   <si>
@@ -164,13 +161,19 @@
     <t>°</t>
   </si>
   <si>
-    <t>Saldo inicial de caja Ingreso de Caja Efectivo USD</t>
+    <t>ESTEBAN TALLAC</t>
   </si>
   <si>
-    <t>Saldo inicial de caja Ingreso de Caja Efectivo $</t>
+    <t>TOTAL del Día</t>
   </si>
   <si>
-    <t>ESTEBAN TALLAC</t>
+    <t xml:space="preserve">Saldo inicial de caja Ingreso de Caja Efectivo </t>
+  </si>
+  <si>
+    <t>Saldo inicial de caja Ingreso de Caja Efectivo</t>
+  </si>
+  <si>
+    <t>TOTA LOCAL</t>
   </si>
 </sst>
 </file>
@@ -420,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -541,6 +544,16 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1377,7 +1390,7 @@
   <dimension ref="A1:L1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -1408,7 +1421,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B3" s="49">
         <v>46094</v>
@@ -1424,7 +1437,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="28">
-        <v>3922100</v>
+        <v>39224.1</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -1435,7 +1448,7 @@
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="28">
         <v>0</v>
@@ -1449,7 +1462,7 @@
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="27">
         <v>5</v>
@@ -1463,7 +1476,7 @@
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="27">
         <v>0</v>
@@ -1476,10 +1489,12 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="29"/>
+      <c r="A8" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="29">
+        <v>131508.85</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -1491,7 +1506,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="28">
-        <v>16847</v>
+        <v>16847.900000000001</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -1501,9 +1516,11 @@
     </row>
     <row r="10" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="B10" s="28">
+        <v>32546.7</v>
+      </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1512,24 +1529,23 @@
     </row>
     <row r="11" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B11" s="28">
-        <v>1932737</v>
+        <v>42890.15</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="52"/>
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="28">
-        <v>206700</v>
+        <v>2067</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -1543,7 +1559,7 @@
     </row>
     <row r="13" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="28">
         <v>68031</v>
@@ -1560,8 +1576,8 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
-        <v>27</v>
+      <c r="A14" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="3"/>
@@ -1575,8 +1591,8 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
-        <v>28</v>
+      <c r="A15" s="53" t="s">
+        <v>27</v>
       </c>
       <c r="B15" s="28"/>
       <c r="C15" s="3"/>
@@ -1591,7 +1607,7 @@
     </row>
     <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="27">
         <v>5</v>
@@ -1608,8 +1624,8 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
-        <v>31</v>
+      <c r="A17" s="53" t="s">
+        <v>30</v>
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="3"/>
@@ -1624,8 +1640,8 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
-        <v>32</v>
+      <c r="A18" s="53" t="s">
+        <v>31</v>
       </c>
       <c r="B18" s="27"/>
       <c r="C18" s="3"/>
@@ -1640,8 +1656,8 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="26" t="s">
-        <v>21</v>
+      <c r="A19" s="54" t="s">
+        <v>20</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1671,13 +1687,13 @@
     </row>
     <row r="21" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="2"/>
@@ -1932,10 +1948,10 @@
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34" s="48">
         <f>SUM(C22:C33)</f>
@@ -1957,13 +1973,13 @@
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="5"/>
@@ -2972,9 +2988,9 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/Caja.xlsx
+++ b/data/Caja.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CajaWeb\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0F6738-1C56-4200-B949-530B10F7BF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7EEC8E-1135-498B-8A3E-45FF47176024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -423,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -548,7 +548,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1528,7 +1527,7 @@
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="51" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="28">
@@ -1537,7 +1536,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="I11" s="52"/>
+      <c r="I11" s="2"/>
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1558,7 +1557,7 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="51" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="28">
@@ -1576,7 +1575,7 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="52" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="28"/>
@@ -1591,7 +1590,7 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="52" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="28"/>
@@ -1606,7 +1605,7 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="51" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="27">
@@ -1624,7 +1623,7 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="52" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="27"/>
@@ -1640,7 +1639,7 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="52" t="s">
         <v>31</v>
       </c>
       <c r="B18" s="27"/>
@@ -1656,7 +1655,7 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="53" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="3"/>

--- a/data/Caja.xlsx
+++ b/data/Caja.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CajaWeb\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7EEC8E-1135-498B-8A3E-45FF47176024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DD7CE5-A993-4D7E-9D28-B9B03E50DB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
